--- a/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Sep_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD2CDFF-D059-4F66-AAD2-C1844100341E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9F3BF8-66A5-400F-B3E0-737A38DF9C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -266,8 +266,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -919,7 +920,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1180,6 +1181,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1531,53 +1535,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="G1" s="101" t="s">
+      <c r="G1" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="104" t="s">
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="104"/>
+      <c r="O1" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="107"/>
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
         <v>46253</v>
       </c>
-      <c r="G2" s="107" t="s">
+      <c r="G2" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="108"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="108" t="s">
+      <c r="H2" s="109"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="108"/>
-      <c r="L2" s="109"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="110"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="107" t="s">
+      <c r="O2" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="109"/>
-      <c r="R2" s="108" t="s">
+      <c r="P2" s="109"/>
+      <c r="Q2" s="110"/>
+      <c r="R2" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="108"/>
-      <c r="T2" s="109"/>
+      <c r="S2" s="109"/>
+      <c r="T2" s="110"/>
       <c r="U2" s="1"/>
       <c r="V2" s="2"/>
     </row>
@@ -2584,11 +2588,11 @@
       <c r="C19" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="98" t="s">
+      <c r="D19" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="99"/>
-      <c r="F19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="101"/>
       <c r="G19" s="40">
         <f>SUM(G4:G18)</f>
         <v>375</v>
@@ -3055,11 +3059,11 @@
       <c r="C25" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="98" t="s">
+      <c r="D25" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="99"/>
-      <c r="F25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="101"/>
       <c r="G25" s="40">
         <f>SUM(G20:G24)</f>
         <v>250</v>
@@ -3436,11 +3440,11 @@
       <c r="C30" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="98" t="s">
+      <c r="D30" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="99"/>
-      <c r="F30" s="100"/>
+      <c r="E30" s="100"/>
+      <c r="F30" s="101"/>
       <c r="G30" s="40">
         <f>SUM(G26:G29)</f>
         <v>2400</v>
@@ -3610,7 +3614,7 @@
     <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="24" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.1796875" bestFit="1" customWidth="1"/>
@@ -3643,35 +3647,35 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.96153846153846156</v>
+        <v>0.15384615384615385</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="F2" s="94">
-        <v>46264</v>
-      </c>
-      <c r="G2" s="107" t="s">
+        <v>46269</v>
+      </c>
+      <c r="G2" s="108" t="s">
         <v>38</v>
       </c>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="104" t="s">
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="110" t="s">
+      <c r="K2" s="106"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="111"/>
+      <c r="P2" s="112"/>
     </row>
     <row r="3" spans="1:17" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="25" t="s">
@@ -3749,34 +3753,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>92+9+11+10+6+12+6+6+12+6+10+14+9+10+19+19+17</f>
-        <v>268</v>
+        <f>5+36</f>
+        <v>41</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.44666666666666666</v>
+        <v>6.8333333333333329E-2</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>318</v>
+        <v>50</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.57818181818181813</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>232</v>
+        <v>500</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>232</v>
+        <v>22.727272727272727</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1865671641791045</v>
+        <v>1.2195121951219512</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3806,38 +3810,37 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>38+8+5+8+8+8+8+8+7+8+9+15+3+18+17</f>
-        <v>168</v>
+        <f>23+33</f>
+        <v>56</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.28000000000000003</v>
+        <v>9.3333333333333338E-2</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>224</v>
+        <v>30</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.49777777777777776</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>226</v>
+        <v>420</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>226</v>
-      </c>
-      <c r="O5" s="72">
+        <v>19.09090909090909</v>
+      </c>
+      <c r="O5" s="98">
         <f t="shared" si="4"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="P5" s="14">
-        <f t="shared" si="4"/>
-        <v>1.7777777777777775</v>
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="P5" s="33">
+        <v>3</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3864,38 +3867,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>32+7+9+6+8+5+9+7+5+6+8+6+6+5+11</f>
-        <v>130</v>
+        <f>6+16</f>
+        <v>22</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>0.21666666666666667</v>
+        <v>3.6666666666666667E-2</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>278</v>
+        <v>28</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0.50545454545454549</v>
+        <v>5.0909090909090911E-2</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>272</v>
+        <v>522</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>272</v>
+        <v>23.727272727272727</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>2.1384615384615384</v>
+        <v>1.2727272727272727</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>2.3328671328671331</v>
+        <v>1.3884297520661157</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3922,38 +3925,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+5+1+6+5+23+3+1+5+8+7+5+1+5+2</f>
-        <v>82</v>
+        <f>2+9</f>
+        <v>11</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>0.13666666666666666</v>
+        <v>1.8333333333333333E-2</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.23749999999999999</v>
+        <v>4.2500000000000003E-2</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>305</v>
+        <v>383</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>305</v>
+        <v>17.40909090909091</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.1585365853658536</v>
+        <v>1.5454545454545454</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.7378048780487805</v>
+        <v>2.3181818181818183</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3980,38 +3983,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>40+5+5+1+5</f>
-        <v>56</v>
+        <f>4+7</f>
+        <v>11</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>9.3333333333333338E-2</v>
+        <v>1.8333333333333333E-2</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>102</v>
+        <v>12.5</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.17739130434782607</v>
+        <v>2.1739130434782608E-2</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>473</v>
+        <v>562.5</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>473</v>
+        <v>25.568181818181817</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.8214285714285714</v>
+        <v>1.1363636363636365</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.9006211180124222</v>
+        <v>1.1857707509881423</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4056,7 +4059,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>550</v>
+        <v>25</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4091,38 +4094,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>22+2+7+3+7+5+6+4+10+5+5+7+2+2+1</f>
-        <v>88</v>
+        <f>2+7</f>
+        <v>9</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.44</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>1671</v>
+        <v>205</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.55700000000000005</v>
+        <v>6.8333333333333329E-2</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>1329</v>
+        <v>2795</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>1329</v>
+        <v>127.04545454545455</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>18.988636363636363</v>
+        <v>22.777777777777779</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.2659090909090911</v>
+        <v>1.5185185185185184</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4148,40 +4151,34 @@
       <c r="G11" s="11">
         <v>600</v>
       </c>
-      <c r="H11" s="12">
-        <f>322+12+10+10+18+12</f>
-        <v>384</v>
-      </c>
+      <c r="H11" s="12"/>
       <c r="I11" s="70">
         <f t="shared" si="0"/>
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="J11" s="11">
         <v>650</v>
       </c>
-      <c r="K11" s="12">
-        <f>370+19+12+20+20+16</f>
-        <v>457</v>
-      </c>
+      <c r="K11" s="12"/>
       <c r="L11" s="71">
         <f t="shared" si="1"/>
-        <v>0.70307692307692304</v>
+        <v>0</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="5"/>
-        <v>193</v>
+        <v>650</v>
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>193</v>
-      </c>
-      <c r="O11" s="72">
+        <v>29.545454545454547</v>
+      </c>
+      <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
-        <v>1.1901041666666667</v>
-      </c>
-      <c r="P11" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P11" s="14" t="e">
         <f t="shared" si="4"/>
-        <v>1.0985576923076923</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q11" s="34"/>
     </row>
@@ -4207,40 +4204,34 @@
       <c r="G12" s="11">
         <v>600</v>
       </c>
-      <c r="H12" s="12">
-        <f>182+7+10+10+13+15+5</f>
-        <v>242</v>
-      </c>
+      <c r="H12" s="12"/>
       <c r="I12" s="70">
         <f t="shared" si="0"/>
-        <v>0.40333333333333332</v>
+        <v>0</v>
       </c>
       <c r="J12" s="11">
         <v>550</v>
       </c>
-      <c r="K12" s="12">
-        <f>185+12+13+30+30+7</f>
-        <v>277</v>
-      </c>
+      <c r="K12" s="12"/>
       <c r="L12" s="71">
         <f t="shared" si="1"/>
-        <v>0.50363636363636366</v>
+        <v>0</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" si="5"/>
-        <v>273</v>
+        <v>550</v>
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>273</v>
-      </c>
-      <c r="O12" s="72">
+        <v>25</v>
+      </c>
+      <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
-        <v>1.1446280991735538</v>
-      </c>
-      <c r="P12" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P12" s="14" t="e">
         <f t="shared" si="4"/>
-        <v>1.2486851990984222</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q12" s="34"/>
     </row>
@@ -4266,40 +4257,34 @@
       <c r="G13" s="11">
         <v>600</v>
       </c>
-      <c r="H13" s="12">
-        <f>15+8+8+8</f>
-        <v>39</v>
-      </c>
+      <c r="H13" s="12"/>
       <c r="I13" s="70">
         <f t="shared" ref="I13:I15" si="7">H13/G13</f>
-        <v>6.5000000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="11">
         <v>450</v>
       </c>
-      <c r="K13" s="12">
-        <f>14+9+6+6</f>
-        <v>35</v>
-      </c>
+      <c r="K13" s="12"/>
       <c r="L13" s="71">
         <f t="shared" ref="L13:L16" si="8">K13/J13</f>
-        <v>7.7777777777777779E-2</v>
+        <v>0</v>
       </c>
       <c r="M13" s="12">
         <f t="shared" si="5"/>
-        <v>415</v>
+        <v>450</v>
       </c>
       <c r="N13" s="14">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>415</v>
-      </c>
-      <c r="O13" s="72">
+        <v>20.454545454545453</v>
+      </c>
+      <c r="O13" s="72" t="e">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
-        <v>0.89743589743589747</v>
-      </c>
-      <c r="P13" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P13" s="14" t="e">
         <f t="shared" ref="P13:P16" si="11">L13/I13</f>
-        <v>1.1965811965811965</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q13" s="34"/>
     </row>
@@ -4323,32 +4308,28 @@
         <v>44</v>
       </c>
       <c r="G14" s="11"/>
-      <c r="H14" s="12">
-        <v>1</v>
-      </c>
+      <c r="H14" s="12"/>
       <c r="I14" s="70" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J14" s="11"/>
-      <c r="K14" s="12">
-        <v>100</v>
-      </c>
+      <c r="K14" s="12"/>
       <c r="L14" s="71" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M14" s="12">
         <f t="shared" si="5"/>
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="14">
         <f t="shared" si="9"/>
-        <v>-100</v>
-      </c>
-      <c r="O14" s="72">
+        <v>0</v>
+      </c>
+      <c r="O14" s="72" t="e">
         <f t="shared" si="10"/>
-        <v>100</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P14" s="14" t="e">
         <f t="shared" si="11"/>
@@ -4425,32 +4406,28 @@
         <v>64</v>
       </c>
       <c r="G16" s="11"/>
-      <c r="H16" s="12">
-        <v>2</v>
-      </c>
+      <c r="H16" s="12"/>
       <c r="I16" s="70" t="e">
         <f t="shared" ref="I16" si="12">H16/G16</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J16" s="11"/>
-      <c r="K16" s="12">
-        <v>1000</v>
-      </c>
+      <c r="K16" s="12"/>
       <c r="L16" s="71" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M16" s="12">
         <f t="shared" si="5"/>
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>-1000</v>
-      </c>
-      <c r="O16" s="72">
+        <v>0</v>
+      </c>
+      <c r="O16" s="72" t="e">
         <f t="shared" si="10"/>
-        <v>500</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P16" s="14" t="e">
         <f t="shared" si="11"/>
@@ -4542,22 +4519,22 @@
       <c r="C19" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="98" t="s">
+      <c r="D19" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="E19" s="99"/>
-      <c r="F19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="101"/>
       <c r="G19" s="40">
         <f>SUM(G4:G18)</f>
         <v>5600</v>
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>1460</v>
+        <v>150</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.26071428571428573</v>
+        <v>2.6785714285714284E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4565,23 +4542,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>4557</v>
+        <v>342.5</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.58990291262135919</v>
+        <v>4.4336569579288027E-2</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>3168</v>
+        <v>7382.5</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>3168</v>
+        <v>335.56818181818181</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.121232876712329</v>
+        <v>2.2833333333333332</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4634,7 +4611,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>465</v>
+        <v>21.136363636363637</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4690,7 +4667,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>467</v>
+        <v>21.227272727272727</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4746,7 +4723,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>464</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4802,7 +4779,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>473</v>
+        <v>21.5</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4858,7 +4835,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>484</v>
+        <v>22</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4879,11 +4856,11 @@
       <c r="C25" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="D25" s="98" t="s">
+      <c r="D25" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="99"/>
-      <c r="F25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="101"/>
       <c r="G25" s="40">
         <f>SUM(G20:G24)</f>
         <v>250</v>
@@ -4914,7 +4891,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>2353</v>
+        <v>106.95454545454545</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4971,7 +4948,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>616</v>
+        <v>28</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -5027,7 +5004,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>566</v>
+        <v>25.727272727272727</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5083,7 +5060,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>574</v>
+        <v>26.09090909090909</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5139,7 +5116,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>612</v>
+        <v>27.818181818181817</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5160,11 +5137,11 @@
       <c r="C30" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="98" t="s">
+      <c r="D30" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="99"/>
-      <c r="F30" s="100"/>
+      <c r="E30" s="100"/>
+      <c r="F30" s="101"/>
       <c r="G30" s="40">
         <f>SUM(G26:G29)</f>
         <v>200</v>
@@ -5195,7 +5172,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>2368</v>
+        <v>107.63636363636364</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5224,11 +5201,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>1661</v>
+        <v>351</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.27454545454545454</v>
+        <v>5.8016528925619835E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5236,23 +5213,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>4836</v>
+        <v>621.5</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.3800392927308448</v>
+        <v>4.8840864440078582E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>7889</v>
+        <v>12103.5</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>7889</v>
+        <v>550.15909090909088</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.9114990969295604</v>
+        <v>1.7706552706552707</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>
